--- a/data/게임샘플.xlsx
+++ b/data/게임샘플.xlsx
@@ -2,39 +2,20 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <workbookPr codeName="현재_통합_문서" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://dap365-my.sharepoint.com/personal/dmcom2_dap365_onmicrosoft_com/Documents/바탕 화면/1234/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\00_AI정보기획 자료\30_AI 프로그램 작업\교육자료\바이브코딩_이론강의\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FB64839D-A488-40CC-9BA5-7B502F7B40DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3587C7B-1C9E-4BE1-9A8A-DBBE2F5C52D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2730" yWindow="345" windowWidth="24195" windowHeight="15855" xr2:uid="{1EA68C61-3E09-4059-9E0A-21CC6E831A4A}"/>
+    <workbookView xWindow="2925" yWindow="0" windowWidth="24195" windowHeight="15855" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="2"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
@@ -78,159 +59,159 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>슈퍼 마리오브라더스</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>마리오 카트 Wii</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Wii 스포츠 리조트</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>포켓몬 레드/포켓몬 블루</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>테트리스</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>뉴 슈퍼 마리오브라더스</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Wii 플레이</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>뉴 슈퍼 마리오브라더스 Wii</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>덕 헌트</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>닌텐독스</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>마리오 카트 DS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>포켓몬 골드/포켓몬 실버</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Wii Fit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Wii Fit 플러스</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>키넥트 어드벤처!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>그랜드 테프트 오토 V</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>그랜드 테프트 오토: 산 안드레아스</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>슈퍼 마리오 월드</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>브레인 에이지: 하루 몇 분 만에 두뇌 훈련하기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>닌텐도 Wii</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>게임보이</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>닌텐도 DS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Xbox 360</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>플스3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>플스2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>슈퍼 닌텐도</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>스포츠</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>횡스크롤</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>레이싱</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>롤플레잉</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>퍼즐</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>기타</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>슈팅</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>시뮬레이션</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>액션</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>닌텐도</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>슈퍼 마리오브라더스</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>닌텐도S</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>횡스크롤</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>마리오 카트 Wii</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>레이싱</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Wii 스포츠 리조트</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>포켓몬 레드/포켓몬 블루</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>게임보이</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>롤플레잉</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>테트리스</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>퍼즐</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>뉴 슈퍼 마리오브라더스</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>닌텐도 DS</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Wii 플레이</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>기타</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>뉴 슈퍼 마리오브라더스 Wii</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>덕 헌트</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>슈팅</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>닌텐독스</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>시뮬레이션</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>마리오 카트 DS</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>포켓몬 골드/포켓몬 실버</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Wii Fit</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Wii Fit 플러스</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>키넥트 어드벤처!</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Xbox 360</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>마이크로소프트</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>그랜드 테프트 오토 V</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>플스3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>액션</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>테이크투</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>그랜드 테프트 오토: 산 안드레아스</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>플스2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>슈퍼 마리오 월드</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>슈퍼 닌텐도</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>브레인 에이지: 하루 몇 분 만에 두뇌 훈련하기</t>
+    <t>닌텐도 NES</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -615,13 +596,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34802B14-E43E-4891-A401-049B588BFF93}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:K21"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5.25" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="43.25" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.75" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="7.125" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="15.125" style="1" bestFit="1" customWidth="1"/>
@@ -672,16 +654,16 @@
         <v>11</v>
       </c>
       <c r="C2" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="D2">
         <v>2006</v>
       </c>
       <c r="E2" t="s">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="F2" t="s">
-        <v>14</v>
+        <v>47</v>
       </c>
       <c r="G2">
         <v>41.49</v>
@@ -704,19 +686,19 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C3" t="s">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="D3">
         <v>1985</v>
       </c>
       <c r="E3" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="F3" t="s">
-        <v>14</v>
+        <v>47</v>
       </c>
       <c r="G3">
         <v>29.08</v>
@@ -739,19 +721,19 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C4" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="D4">
         <v>2008</v>
       </c>
       <c r="E4" t="s">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="F4" t="s">
-        <v>14</v>
+        <v>47</v>
       </c>
       <c r="G4">
         <v>15.85</v>
@@ -774,19 +756,19 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="D5">
         <v>2009</v>
       </c>
       <c r="E5" t="s">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="F5" t="s">
-        <v>14</v>
+        <v>47</v>
       </c>
       <c r="G5">
         <v>15.75</v>
@@ -809,19 +791,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C6" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="D6">
         <v>1996</v>
       </c>
       <c r="E6" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="F6" t="s">
-        <v>14</v>
+        <v>47</v>
       </c>
       <c r="G6">
         <v>11.27</v>
@@ -844,19 +826,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="C7" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="D7">
         <v>1989</v>
       </c>
       <c r="E7" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="F7" t="s">
-        <v>14</v>
+        <v>47</v>
       </c>
       <c r="G7">
         <v>23.2</v>
@@ -879,19 +861,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C8" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="D8">
         <v>2006</v>
       </c>
       <c r="E8" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="F8" t="s">
-        <v>14</v>
+        <v>47</v>
       </c>
       <c r="G8">
         <v>11.38</v>
@@ -914,19 +896,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="C9" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="D9">
         <v>2006</v>
       </c>
       <c r="E9" t="s">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="F9" t="s">
-        <v>14</v>
+        <v>47</v>
       </c>
       <c r="G9">
         <v>14.03</v>
@@ -949,19 +931,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="C10" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="D10">
         <v>2009</v>
       </c>
       <c r="E10" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="F10" t="s">
-        <v>14</v>
+        <v>47</v>
       </c>
       <c r="G10">
         <v>14.59</v>
@@ -984,19 +966,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="C11" t="s">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="D11">
         <v>1984</v>
       </c>
       <c r="E11" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="F11" t="s">
-        <v>14</v>
+        <v>47</v>
       </c>
       <c r="G11">
         <v>26.93</v>
@@ -1019,19 +1001,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
+        <v>21</v>
+      </c>
+      <c r="C12" t="s">
         <v>33</v>
-      </c>
-      <c r="C12" t="s">
-        <v>27</v>
       </c>
       <c r="D12">
         <v>2005</v>
       </c>
       <c r="E12" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="F12" t="s">
-        <v>14</v>
+        <v>47</v>
       </c>
       <c r="G12">
         <v>9.07</v>
@@ -1054,19 +1036,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="C13" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="D13">
         <v>2005</v>
       </c>
       <c r="E13" t="s">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="F13" t="s">
-        <v>14</v>
+        <v>47</v>
       </c>
       <c r="G13">
         <v>9.81</v>
@@ -1089,19 +1071,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="C14" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="D14">
         <v>1999</v>
       </c>
       <c r="E14" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="F14" t="s">
-        <v>14</v>
+        <v>47</v>
       </c>
       <c r="G14">
         <v>9</v>
@@ -1124,19 +1106,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="C15" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="D15">
         <v>2007</v>
       </c>
       <c r="E15" t="s">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="F15" t="s">
-        <v>14</v>
+        <v>47</v>
       </c>
       <c r="G15">
         <v>8.94</v>
@@ -1159,19 +1141,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="C16" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="D16">
         <v>2009</v>
       </c>
       <c r="E16" t="s">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="F16" t="s">
-        <v>14</v>
+        <v>47</v>
       </c>
       <c r="G16">
         <v>9.09</v>
@@ -1194,19 +1176,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="C17" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="D17">
         <v>2010</v>
       </c>
       <c r="E17" t="s">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="F17" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="G17">
         <v>14.97</v>
@@ -1229,19 +1211,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="C18" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="D18">
         <v>2013</v>
       </c>
       <c r="E18" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F18" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="G18">
         <v>7.01</v>
@@ -1264,19 +1246,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="C19" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="D19">
         <v>2004</v>
       </c>
       <c r="E19" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F19" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="G19">
         <v>9.43</v>
@@ -1299,19 +1281,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="C20" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="D20">
         <v>1990</v>
       </c>
       <c r="E20" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="F20" t="s">
-        <v>14</v>
+        <v>47</v>
       </c>
       <c r="G20">
         <v>12.78</v>
@@ -1334,19 +1316,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="C21" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="D21">
         <v>2005</v>
       </c>
       <c r="E21" t="s">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="F21" t="s">
-        <v>14</v>
+        <v>47</v>
       </c>
       <c r="G21">
         <v>4.75</v>
